--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4432100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4435200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3938400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3983400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3893400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3972800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3664500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3736500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3507100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3718800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3827500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3737400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3310900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3646200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3574400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3374800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3219600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3252600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3358200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3154400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2917600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2856000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2750800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2749500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2679700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2691800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2422800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2253600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2207400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2203400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1308600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1359100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1408900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1430100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1373500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1426200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1435200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1387600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1299500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1362200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1454700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1412200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1328700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1477600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1707200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1475900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1420400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1480100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1578400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1475500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1327000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1317500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1368900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1292700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1236700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1212300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1131300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1041700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1025400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1021300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>92700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>830800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>969100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>985300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>913700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>819600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3123500</v>
+      </c>
+      <c r="E10" s="3">
         <v>3076100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2529500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2553300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2520000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2546600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2229400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2348900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2207600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2356600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2372800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2325200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1982200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2168600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1867200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1898900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1799100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1772400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1779800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1678900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1590600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1538500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1381900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1456800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1443000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1479400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1291500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1211900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1182000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1182200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>854200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>852600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>882700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>999800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>940000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>683700</v>
+      </c>
+      <c r="E12" s="3">
         <v>649800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>634000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>638000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>608100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>604500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>612400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>630800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>613200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>578200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>631700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>595800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>539000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>545900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>576600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>548400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>497900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>469200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>530100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>534700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>484300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>426000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>421700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>411000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>354900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>338000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>349100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>332900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>297300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>311300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>269400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>300500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>275100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>209300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>184400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>171100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>156000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>137200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>127600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,13 +1496,16 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>37</v>
+      <c r="D14" s="3">
+        <v>434800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>37</v>
@@ -1523,8 +1543,8 @@
       <c r="P14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E15" s="3">
         <v>62400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>103000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>86800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>59800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>66300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>95600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>74200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>87000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>78700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>93000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>89300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>91200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>157600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2652400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2749000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2857800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2628600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2533900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2593000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2717700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2544800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2663100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2858800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2701600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2474900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2595100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2949400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2719700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2531900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2492200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2723300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2617800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2383300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2260800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2331600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2326500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2065200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1984000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1964500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1740100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1638400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1629700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>531600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1779700</v>
+      </c>
+      <c r="E18" s="3">
         <v>1835000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1189400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1125600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1264800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1438900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1071600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1018900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>962400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1055700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>968600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1035800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>836000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1051100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>625000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>655100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>687600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>760400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>634900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>536600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>534200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>595200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>419300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>422900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>614500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>707800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>458300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>513500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>569000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>573700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>566600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>354900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>334800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>173200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>211700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>378400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>505400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>708200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>562300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,263 +2085,270 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E20" s="3">
         <v>26600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>31000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-42700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-248600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>144300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>53000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>22000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-218700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>18700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>48300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>478800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>274000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>50600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>118200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>210400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-212200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>39200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>227800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>86200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>152700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>140900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>55000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>49800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>68900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>55200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>50200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>24600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>32300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>43400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>27100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>105700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1789400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1870900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1287800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1181400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1367400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1540600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1415700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>948800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1028200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1163300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1008600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1103200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1145800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1189900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>781800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1232600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>881400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>870100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1024100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>701700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>768200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>919700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>341000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>596700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>973700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>902800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>718200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>762700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>720800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>712200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>734400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>489200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>452600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>208600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>277000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>441900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>574100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>756900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>682100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3">
         <v>47800</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>37</v>
@@ -2316,11 +2356,11 @@
       <c r="H22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="3">
         <v>81900</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>37</v>
@@ -2328,11 +2368,11 @@
       <c r="L22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="3">
         <v>124700</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>37</v>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1417000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1938300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1089500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1420000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1486500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1716000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1411700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1139900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1118700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1286400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1092200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1247300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1223300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1214000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>673400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1134000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>796800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>764300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>908900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>587200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>652400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>805600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>207100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>462100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>842300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>794000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>611000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>654400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>624000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>623500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>635400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>410100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>385000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>156000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>236300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>410700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>548800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>735300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>668100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E24" s="3">
         <v>365900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>178800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>184900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>217900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>262500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>189800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>183800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>179000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>205800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>150700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>176800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>98200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>237100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>136300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>219200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>175100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>168400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>128700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>114800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>158200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>177300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>76900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>50500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>156900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>170700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>134900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>104500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>193500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>132800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>118000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>40600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>43100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>33500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>104400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>140000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>128300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1572400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>910700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1235100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1268700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1453400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1221900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>956100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>939700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1080600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>941500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1070500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1125100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>976900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>537100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>914800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>621700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>595900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>780200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>472400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>494200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>628300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>130100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>411600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>685400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>623300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>476100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>640900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>519600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>429900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>502600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>292100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>324700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>115500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>193200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>377200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>444400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>595300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>539800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1027700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1547600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>892400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1210200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1419600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1201000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>932100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>930100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1057300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>928300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1074000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1136600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>983300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>557300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>925600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>648800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>606700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>784500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>452300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>503500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>617900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>135800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>441800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>668700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>560200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>470200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>636600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>512500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>417500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>489400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>288700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>302200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>107900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>190800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>375100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>441100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>582200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>535600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3201,16 +3262,16 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>86900</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>37</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>37</v>
@@ -3218,14 +3279,14 @@
       <c r="X29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3234,28 +3295,28 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1323600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-43200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-53600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
+      <c r="AK29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AL29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-26600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-31000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>42700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>248600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-144300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-53000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-22000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>218700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-48300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-478800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-274000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-50600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-118200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-210400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>212200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-39200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-227800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-86200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-152700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-140900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>17100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1027700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1547600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>892400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1210200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1419600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1201000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>932100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>930100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1057300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>928300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1074000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1136600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>983300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>557300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>925600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>735600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>606700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>784500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>452300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>503500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>617900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>135800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>441800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>668700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>560200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>470200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1960200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>469200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>363900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>246600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>223400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>302200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>107900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>190800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>375100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>441100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>582200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>535600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1027700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1547600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>892400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1210200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1419600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1201000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>932100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>930100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1057300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>928300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1074000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1136600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>983300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>557300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>925600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>735600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>606700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>784500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>452300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>503500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>617900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>135800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>441800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>668700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>560200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>470200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1960200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>469200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>363900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>246600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>223400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>302200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>107900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>190800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>375100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>441100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>582200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>535600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4219,481 +4305,491 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3358600</v>
+      </c>
+      <c r="E41" s="3">
         <v>7367300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6743700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4400300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7598000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5753300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7039700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2877500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2612200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5959000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3022000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2071700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1760300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1994500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3508900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2486800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2288500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1360400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1997600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3165200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1412400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1223700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1269100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>952900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1565400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>882300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>499900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>422100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>738300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>631300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>724500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>668700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>441800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>534800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>410200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>382200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>447100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>587600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>791100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>22461800</v>
+      </c>
+      <c r="E42" s="3">
         <v>17410700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16738000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16542100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12878400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13555600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11821900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>14798300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14294100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12681800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14860400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13117100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13380800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15539500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13050600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13572300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13218500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12793000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11440800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9817800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12928100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>12628000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>11741800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>13547400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>12606300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11025600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10593800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>9029400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7748900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7283200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>845900</v>
+      </c>
+      <c r="E43" s="3">
         <v>941400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1029200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>837500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>806300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>929100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1117700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>880000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>875900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1075800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1304800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>889800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>736700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>886800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>705300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>719500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>724700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>728700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>758900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>770800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>632900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>703900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>637000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>729300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>739500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>719300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>642000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>724700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>686700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>774700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>598200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>639500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>554400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>637900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>537200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>483700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>505200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>546600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>618300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E44" s="3">
         <v>79200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>98500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>89500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>82600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>71400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>87500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>83600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>98100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>98900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>111300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>127600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>140100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>128900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>117300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>118900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>132900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>147600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>125700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>121800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>86500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>77300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>82300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>88700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>100200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>105700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>606000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>653500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>154800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>880500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>814400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>734800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AL44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AM44" s="3" t="s">
         <v>37</v>
@@ -4701,547 +4797,562 @@
       <c r="AN44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AO44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP44" s="3">
         <v>229500</v>
       </c>
-      <c r="AP44" s="3" t="s">
+      <c r="AQ44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>878200</v>
+      </c>
+      <c r="E45" s="3">
         <v>900800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>964000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>860200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>917000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>971000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>755200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>799100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>888500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>738100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>735300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1148600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1273300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1446800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1440700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1255600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1584900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1384500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1404200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1275600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1457600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1380100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1517400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1268600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2428400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1379700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1603500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28274600</v>
+      </c>
+      <c r="E46" s="3">
         <v>27352100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25822900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24049000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22746300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21728200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21006000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20041200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19011300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21022400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20123300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17482900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17128900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19732600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18553400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18180800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17795800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16441700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15585700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15486300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16483600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16081600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15010100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16764400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16373600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14233300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13104500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12710400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11159600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10946200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3179300</v>
+      </c>
+      <c r="E47" s="3">
         <v>441500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3067900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>399600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>409700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>416900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3182800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>573800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>542200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>145400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3220100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>304400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>369800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>397700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3033600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>618100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>622000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>617700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3393300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>988400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1009300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>938200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2553100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>626300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1005500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>607400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1794500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7700</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>7600</v>
       </c>
       <c r="AF47" s="3">
         <v>7600</v>
       </c>
       <c r="AG47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AH47" s="3">
         <v>776400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>21500</v>
       </c>
       <c r="AJ47" s="3">
         <v>21500</v>
       </c>
       <c r="AK47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AL47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AL47" s="3">
-        <v>7400</v>
       </c>
       <c r="AM47" s="3">
         <v>7400</v>
       </c>
       <c r="AN47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AO47" s="3">
         <v>74200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>366500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1204300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1205000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1250400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1196400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1179100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1165100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1241400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1169100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1113500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1115800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1244500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1039200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1013100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>963400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1019300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>851800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>837200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>806700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>892500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>704600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>667300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>647500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>741700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>654200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>650800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1302800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1353900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1301600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>945300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>944100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>678700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>742600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>699200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>611500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>559400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>498100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>442500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>398600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>351900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>586200</v>
+      </c>
+      <c r="E49" s="3">
         <v>582100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>979400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>572900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>573900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>570700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1019400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>599500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>553500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>560700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1102100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>563200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>571900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>600100</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5287,38 +5398,41 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-      <c r="AG49" s="3" t="s">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>492700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>84200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>84700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>88000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>88500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>86500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>86900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>85600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>543200</v>
+      </c>
+      <c r="E52" s="3">
         <v>3548100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>128400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3543400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3889700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3622000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>247000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3808400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3802200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3966700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>305300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3929800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3886300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4069300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1749500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4210700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4125300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4122900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1297500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3828800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3852800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3282900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1444000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3282800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3215000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2575400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1012100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2275000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2065600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2072100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>773500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>287400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>544500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>588900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>726800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>453800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34184500</v>
+      </c>
+      <c r="E54" s="3">
         <v>33548400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31656000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30128200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29104500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27679800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26851500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26359200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25229800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27015400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26220200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23514400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23152100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25947900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24355800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23861300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23380300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21989000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21169100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21008100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22012900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20950100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19748900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21327700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21244900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18718800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17264900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16294800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14178000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13970100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,496 +6145,509 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E57" s="3">
         <v>113200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>92000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>77900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>98700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>107700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>109000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>120700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>118300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>102100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>121000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>212500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>119800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>131000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>127700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>135700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>156200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>126500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>149100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>157900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>146900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>125800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>188800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>186700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>187800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>398700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>450600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>174500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>360300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>331200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>339400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>362500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>307000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>281800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>234400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>203000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1855500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1588300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>929000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1032400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1574100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1353800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1640800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1510300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1814700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3440700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2750000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1537900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1638300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3987800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3366000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3515600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3896300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3131600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2666400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2788200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3864800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3038300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2715100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3278400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3232000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3096000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2591200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2385900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2070800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2159500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>983000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>850800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>798100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>665400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>554900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3388500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3998200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4704000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3341100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2898300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3074000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3413900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2587500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2201400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2597600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3128900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2365600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2137800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2408600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4433300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4243700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3958700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3888400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4156000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4022200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3733400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3862800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3633700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3490100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3302200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3563100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3110800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2755700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2714800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2925100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8187800</v>
+      </c>
+      <c r="E60" s="3">
         <v>8327400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7487300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7035700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7042600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6771600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6804600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6516800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6320100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8316500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7593200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6012200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5838000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8469800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8011700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7879100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7986000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7147600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6958100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6966500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7724700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7050200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6506700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6915400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6660000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6848000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5888700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5329300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5184200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5535100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6512,11 +6655,11 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>33200</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -6524,47 +6667,47 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>115200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>61000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>138700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>545200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>543000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>515300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>490500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>466500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>438300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>175700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -6625,130 +6768,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E62" s="3">
         <v>199800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>176400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>170000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>162500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>111800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>170900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>164100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>172900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>100900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>181900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>156900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>169600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>479900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>342600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>343700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>350100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>336700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>331200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>284400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>241500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>186100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>154400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>214700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>166100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>129300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>185900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>210400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>168600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>65000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>87600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>84800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>60500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>34400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>41800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>27800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>57100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8928000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8995800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8050900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7522900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7593000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7302300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7329300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7009500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6742500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8922700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8157100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6527700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6844700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9545200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9590800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9304100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9362800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8502500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8034800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9098800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9768700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9019800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8316900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8765700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8600700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8843500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7802300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6535300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6393700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6672100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,19 +7938,22 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="3">
+        <v>23785200</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21762000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>37</v>
@@ -7787,11 +7961,11 @@
       <c r="H72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="3">
         <v>18123900</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>37</v>
@@ -7799,11 +7973,11 @@
       <c r="L72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" s="3">
         <v>16042500</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>37</v>
@@ -7811,11 +7985,11 @@
       <c r="P72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R72" s="3">
         <v>13020000</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>37</v>
@@ -7823,11 +7997,11 @@
       <c r="T72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>37</v>
@@ -7835,11 +8009,11 @@
       <c r="X72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>37</v>
@@ -7847,11 +8021,11 @@
       <c r="AB72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>37</v>
@@ -7859,11 +8033,11 @@
       <c r="AF72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="AH72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>37</v>
@@ -7883,14 +8057,17 @@
       <c r="AN72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24598200</v>
+      </c>
+      <c r="E76" s="3">
         <v>23881800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22917800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21948600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20881000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19821400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19000400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18839600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18014500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17627000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17527500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16443100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15755700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15815800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14765000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14557200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14017500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13486500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13134300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11909300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12244200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11930300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11432100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12562000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12644200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9875400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9462600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9759400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7784300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7298000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1027700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1547600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>892400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1210200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1419600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1201000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>932100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>930100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1057300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>928300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1074000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1136600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>983300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>557300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>925600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>735600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>606700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>784500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>452300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>503500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>617900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>135800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>441800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>668700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>560200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>470200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1960200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>469200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>363900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>246600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>223400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>302200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>107900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>190800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>375100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>441100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>582200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>535600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E83" s="3">
         <v>66300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>80100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>74200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>87000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>78700</v>
       </c>
       <c r="I83" s="3">
         <v>78700</v>
       </c>
       <c r="J83" s="3">
+        <v>78700</v>
+      </c>
+      <c r="K83" s="3">
         <v>89300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>91200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>157600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>98200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>90900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>120900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>108400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>98600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>84700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>105800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>115200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>114500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>115800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>114100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>134000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>134500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>131500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>108900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>107100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>106000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>98100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>89700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>98200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>79800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>67600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>52600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>40700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>31300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>25300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>21700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>14100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1468200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1991100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2119300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1818700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1516200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1668400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1782700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1507700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>898800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1323600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1665300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1349100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1058800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>873600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1270100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1034300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>921900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>632800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1153000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>894500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>671300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>771500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1143400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>795900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>703200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1025500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>848500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>593400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>682300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>517400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>862000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>506300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>280900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>273300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>576000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>245700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>344500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>598300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>782200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-45300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-68400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-88100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-71800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-95100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-510800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-709300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-530200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-893200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-739700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-625900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-988600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-45900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-51700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-50800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5102200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>55400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3458300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>543400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1769600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2826200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-102800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2043700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1781000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1512500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-70700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1598000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2531900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>544800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>136400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-164500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3007600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-788000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-991800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>145500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-391000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-514900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-724400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>462100</v>
+      </c>
+      <c r="E96" s="3">
         <v>747600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>368200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>362900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>430200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>769600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>271600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>281300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>311700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>684900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>318600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>332100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>292200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>176500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-284600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-223500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-195100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-232500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-129600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-146100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-181800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-36300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-119900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-203000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-164300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-146200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-142200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-93700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-468500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-260600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-504500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-897800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-272400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1142200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-337400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1205900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2190600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-68600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>724800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-939300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2802600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>83300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-871600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-992700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>116900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>316100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-147900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>281100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>195600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-887500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-367800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2973500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-219900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>180400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>112800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-188300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>62800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>406100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>16300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>17200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-24600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>11200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-11100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>26500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>11700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>7600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>9900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4130200</v>
+      </c>
+      <c r="E102" s="3">
         <v>555300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1645100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2554000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1782800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1251200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4287000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>189300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3334300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3030100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>853000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>339700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-152400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1572800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>950800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>178500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>884700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-578200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1786900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>160900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>392000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-681100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>718200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>426300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-44800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-378000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>70400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>330100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>114500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>139300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-112800</v>
       </c>
     </row>
